--- a/access_control_forms/014_mailbox_usage_log--access_control_forms.xlsx
+++ b/access_control_forms/014_mailbox_usage_log--access_control_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -742,8 +742,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,12 +771,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'6-1',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '6-1', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'6-2',_'label':_'physical'}</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '6-2', 'label': 'Physical'}</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'6-3',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '6-3', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'7-1',_'label':_'read'}</t>
+          <t>read</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '7-1', 'label': 'Read'}</t>
+          <t>Read</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'7-2',_'label':_'write'}</t>
+          <t>write</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '7-2', 'label': 'Write'}</t>
+          <t>Write</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'7-3',_'label':_'delete'}</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '7-3', 'label': 'Delete'}</t>
+          <t>Delete</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'8-1',_'label':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '8-1', 'label': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'8-2',_'label':_'close'}</t>
+          <t>close</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '8-2', 'label': 'Close'}</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'8-3',_'label':_'delete'}</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '8-3', 'label': 'Delete'}</t>
+          <t>Delete</t>
         </is>
       </c>
     </row>
